--- a/AdvanceExcel/ChooseDemo01.xlsx
+++ b/AdvanceExcel/ChooseDemo01.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Practice\For Golu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C10040A-55F7-4890-8048-224B12CB361B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DF35E4-21E0-43CB-B2E3-4F3E837228E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{14135FCB-110C-47DE-857A-0A37F4E546E4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{14135FCB-110C-47DE-857A-0A37F4E546E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Gold" sheetId="2" r:id="rId2"/>
     <sheet name="Silver" sheetId="3" r:id="rId3"/>
     <sheet name="Pletinum" sheetId="4" r:id="rId4"/>
+    <sheet name="Sales_Data" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Gold">Gold!$A$2:$B$6</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="28">
   <si>
     <t>Item Name</t>
   </si>
@@ -110,13 +111,31 @@
   </si>
   <si>
     <t>Data Set No</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Index</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +148,14 @@
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,12 +193,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,7 +586,7 @@
         <v>55000</v>
       </c>
       <c r="E2" s="2">
-        <f>VLOOKUP(D2,CHOOSE(VLOOKUP(B2,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" ref="E2:E14" si="0">VLOOKUP(D2,CHOOSE(VLOOKUP(B2,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
         <v>5000</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -577,7 +610,7 @@
         <v>85000</v>
       </c>
       <c r="E3" s="2">
-        <f>VLOOKUP(D3,CHOOSE(VLOOKUP(B3,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -601,7 +634,7 @@
         <v>130000</v>
       </c>
       <c r="E4" s="2">
-        <f>VLOOKUP(D4,CHOOSE(VLOOKUP(B4,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>12000</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -625,7 +658,7 @@
         <v>150000</v>
       </c>
       <c r="E5" s="2">
-        <f>VLOOKUP(D5,CHOOSE(VLOOKUP(B5,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
@@ -643,7 +676,7 @@
         <v>18000</v>
       </c>
       <c r="E6" s="2">
-        <f>VLOOKUP(D6,CHOOSE(VLOOKUP(B6,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
     </row>
@@ -661,7 +694,7 @@
         <v>30000</v>
       </c>
       <c r="E7" s="2">
-        <f>VLOOKUP(D7,CHOOSE(VLOOKUP(B7,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
     </row>
@@ -679,7 +712,7 @@
         <v>45000</v>
       </c>
       <c r="E8" s="2">
-        <f>VLOOKUP(D8,CHOOSE(VLOOKUP(B8,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
     </row>
@@ -697,7 +730,7 @@
         <v>60000</v>
       </c>
       <c r="E9" s="2">
-        <f>VLOOKUP(D9,CHOOSE(VLOOKUP(B9,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
     </row>
@@ -715,7 +748,7 @@
         <v>40000</v>
       </c>
       <c r="E10" s="2">
-        <f>VLOOKUP(D10,CHOOSE(VLOOKUP(B10,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
     </row>
@@ -733,7 +766,7 @@
         <v>70000</v>
       </c>
       <c r="E11" s="2">
-        <f>VLOOKUP(D11,CHOOSE(VLOOKUP(B11,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
     </row>
@@ -751,7 +784,7 @@
         <v>100000</v>
       </c>
       <c r="E12" s="2">
-        <f>VLOOKUP(D12,CHOOSE(VLOOKUP(B12,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
     </row>
@@ -769,7 +802,7 @@
         <v>150000</v>
       </c>
       <c r="E13" s="2">
-        <f>VLOOKUP(D13,CHOOSE(VLOOKUP(B13,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>7000</v>
       </c>
     </row>
@@ -787,7 +820,7 @@
         <v>25000</v>
       </c>
       <c r="E14" s="2">
-        <f>VLOOKUP(D14,CHOOSE(VLOOKUP(B14,$J$1:$K$4,2,0),Gold,Silver,Pletinum),2,1)</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
     </row>
@@ -977,4 +1010,254 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64EDE91-1D85-45C0-93BD-91C29262A230}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="91.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>95000</v>
+      </c>
+      <c r="F3" s="5">
+        <f>SUM(CHOOSE(VLOOKUP(F2,$H$2:$I$5,2,0),SUM(D2:D13),AVERAGE(D2:D13),MAX(D2:D13),MIN(D2:D13)))</f>
+        <v>928000</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(F3)</f>
+        <v>=SUM(CHOOSE(VLOOKUP(F2,$H$2:$I$5,2,0),SUM(D2:D13),AVERAGE(D2:D13),MAX(D2:D13),MIN(D2:D13)))</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2">
+        <v>120000</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>40</v>
+      </c>
+      <c r="D9" s="2">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2">
+        <v>150000</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{32AF1F45-A9C4-4B94-A608-3A2191D88BD6}">
+      <formula1>$H$2:$H$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>